--- a/data/trans_bre/IP19C07-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP19C07-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,07; 7,02</t>
+          <t>-11,18; 6,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,94; 10,66</t>
+          <t>-7,39; 9,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,04; 9,11</t>
+          <t>-6,08; 9,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,27; 14,94</t>
+          <t>-0,09; 13,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-56,64; 71,19</t>
+          <t>-57,3; 66,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-50,39; 203,51</t>
+          <t>-52,04; 168,61</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-60,0; 275,44</t>
+          <t>-62,03; 303,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-39,46; —</t>
+          <t>-55,88; —</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,48; 4,52</t>
+          <t>-7,17; 4,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 8,17</t>
+          <t>-4,19; 8,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,21; 13,74</t>
+          <t>1,55; 12,56</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 4,6</t>
+          <t>-5,2; 5,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-57,73; 73,57</t>
+          <t>-56,35; 78,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-37,45; 152,67</t>
+          <t>-37,56; 150,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,95; 866,25</t>
+          <t>15,24; 1046,72</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-71,32; 141,14</t>
+          <t>-70,85; 165,36</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 10,5</t>
+          <t>-3,78; 10,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 6,95</t>
+          <t>-7,53; 6,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 3,1</t>
+          <t>-7,29; 3,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 8,29</t>
+          <t>-4,97; 8,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-43,36; 291,84</t>
+          <t>-45,56; 278,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-60,41; 128,95</t>
+          <t>-64,0; 129,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-80,39; 137,44</t>
+          <t>-83,05; 106,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-51,38; 165,82</t>
+          <t>-45,28; 187,07</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,65; 18,16</t>
+          <t>0,8; 16,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-10,78; 3,42</t>
+          <t>-11,7; 2,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 9,26</t>
+          <t>-4,53; 8,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 10,13</t>
+          <t>-3,92; 9,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 304,37</t>
+          <t>0,18; 356,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-68,02; 43,69</t>
+          <t>-69,52; 36,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-44,48; 200,57</t>
+          <t>-48,74; 188,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-40,87; 300,86</t>
+          <t>-43,75; 278,59</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 5,99</t>
+          <t>-1,62; 5,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 3,38</t>
+          <t>-3,7; 3,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 5,7</t>
+          <t>-0,67; 5,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 5,24</t>
+          <t>-0,94; 5,13</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-13,72; 74,04</t>
+          <t>-13,8; 71,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-31,73; 41,55</t>
+          <t>-31,59; 47,55</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-12,12; 130,64</t>
+          <t>-10,35; 134,34</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-15,36; 119,51</t>
+          <t>-14,57; 119,18</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C07-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP19C07-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,18; 6,91</t>
+          <t>-10,96; 6,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,39; 9,56</t>
+          <t>-6,92; 9,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 9,53</t>
+          <t>-5,79; 9,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 13,27</t>
+          <t>-0,32; 13,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-57,3; 66,68</t>
+          <t>-55,83; 65,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-52,04; 168,61</t>
+          <t>-51,94; 163,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-62,03; 303,79</t>
+          <t>-55,89; 258,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-55,88; —</t>
+          <t>-54,22; 2089,09</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 4,61</t>
+          <t>-7,57; 4,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 8,47</t>
+          <t>-4,65; 8,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,55; 12,56</t>
+          <t>1,47; 12,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 5,17</t>
+          <t>-5,07; 4,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-56,35; 78,53</t>
+          <t>-62,98; 70,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-37,56; 150,42</t>
+          <t>-39,66; 167,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,24; 1046,72</t>
+          <t>9,69; 951,72</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-70,85; 165,36</t>
+          <t>-67,14; 173,53</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 10,47</t>
+          <t>-4,11; 10,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 6,81</t>
+          <t>-8,11; 6,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 3,28</t>
+          <t>-7,72; 3,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 8,45</t>
+          <t>-5,15; 8,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-45,56; 278,86</t>
+          <t>-44,24; 261,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-64,0; 129,27</t>
+          <t>-64,1; 140,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-83,05; 106,34</t>
+          <t>-81,4; 228,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-45,28; 187,07</t>
+          <t>-48,6; 159,72</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,8; 16,87</t>
+          <t>1,23; 17,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,7; 2,82</t>
+          <t>-11,54; 3,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 8,46</t>
+          <t>-3,94; 8,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 9,35</t>
+          <t>-3,35; 9,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,18; 356,82</t>
+          <t>1,15; 307,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-69,52; 36,12</t>
+          <t>-69,03; 42,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-48,74; 188,58</t>
+          <t>-46,83; 192,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-43,75; 278,59</t>
+          <t>-40,38; 262,85</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 5,96</t>
+          <t>-1,33; 5,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 3,63</t>
+          <t>-3,68; 3,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 5,6</t>
+          <t>-0,57; 5,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 5,13</t>
+          <t>-0,93; 5,24</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-13,8; 71,75</t>
+          <t>-11,63; 67,62</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-31,59; 47,55</t>
+          <t>-32,31; 43,71</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-10,35; 134,34</t>
+          <t>-10,83; 126,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-14,57; 119,18</t>
+          <t>-15,92; 117,42</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C07-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP19C07-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5,36</t>
+          <t>5,34</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>244,46%</t>
+          <t>239,85%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,96; 6,84</t>
+          <t>-12,07; 7,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 9,64</t>
+          <t>-6,94; 10,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 9,01</t>
+          <t>-6,04; 9,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 13,05</t>
+          <t>0,03; 14,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-55,83; 65,28</t>
+          <t>-56,64; 71,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-51,94; 163,9</t>
+          <t>-50,39; 203,51</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-55,89; 258,82</t>
+          <t>-60,0; 275,44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-54,22; 2089,09</t>
+          <t>-41,95; —</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,34</t>
+          <t>-0,39</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-6,14%</t>
+          <t>-6,62%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,57; 4,16</t>
+          <t>-7,48; 4,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 8,55</t>
+          <t>-4,38; 8,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,47; 12,74</t>
+          <t>2,21; 13,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 4,86</t>
+          <t>-5,91; 4,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-62,98; 70,98</t>
+          <t>-57,73; 73,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-39,66; 167,77</t>
+          <t>-37,45; 152,67</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,69; 951,72</t>
+          <t>17,95; 866,25</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-67,14; 173,53</t>
+          <t>-71,03; 139,2</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,31</t>
+          <t>1,39</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,0%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 10,63</t>
+          <t>-4,07; 10,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,11; 6,94</t>
+          <t>-7,11; 6,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,72; 3,93</t>
+          <t>-6,99; 3,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 8,01</t>
+          <t>-6,03; 8,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-44,24; 261,2</t>
+          <t>-43,36; 291,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-64,1; 140,29</t>
+          <t>-60,41; 128,95</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-81,4; 228,73</t>
+          <t>-80,39; 137,44</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-48,6; 159,72</t>
+          <t>-50,48; 169,0</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,75</t>
+          <t>2,37</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>35,96%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,23; 17,34</t>
+          <t>0,65; 18,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,54; 3,28</t>
+          <t>-10,78; 3,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 8,94</t>
+          <t>-3,92; 9,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 9,31</t>
+          <t>-3,58; 9,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,15; 307,94</t>
+          <t>-1,24; 304,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-69,03; 42,38</t>
+          <t>-68,02; 43,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-46,83; 192,96</t>
+          <t>-44,48; 200,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-40,38; 262,85</t>
+          <t>-45,25; 276,33</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,0</t>
+          <t>1,89</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>31,17%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 5,87</t>
+          <t>-1,57; 5,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 3,59</t>
+          <t>-3,53; 3,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 5,75</t>
+          <t>-0,68; 5,7</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 5,24</t>
+          <t>-1,33; 5,24</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-11,63; 67,62</t>
+          <t>-13,72; 74,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-32,31; 43,71</t>
+          <t>-31,73; 41,55</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-10,83; 126,84</t>
+          <t>-12,12; 130,64</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-15,92; 117,42</t>
+          <t>-19,25; 111,24</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C07-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP19C07-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,197 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-2,01</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1,09</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1,4</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5,34</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-13,07%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>11,02%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>19,94%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>239,85%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-2.009068714560355</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>1.093756552460445</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>1.403716844530478</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>5.338598625451309</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.130668649406775</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.1102028093618243</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.1994248339676603</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>2.398487834329382</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-12,07; 7,02</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-6,94; 10,66</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-6,04; 9,11</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0,03; 14,41</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-56,64; 71,19</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-50,39; 203,51</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-60,0; 275,44</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-41,95; —</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-12.06865486188864</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-6.935750688037645</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-6.043501822551018</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>0.0326126828867021</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.5664274601359003</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.5038760577973337</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.6000115959340716</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.4195012461963249</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>7.020188101622302</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>10.66006819422456</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>9.113124440697304</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>14.4052876459903</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.7118977568172125</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>2.035083680302393</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>2.754416997648481</v>
+      </c>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-1,24</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2,05</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>6,86</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-0,39</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-13,33%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>24,01%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>225,6%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-6,62%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-7,48; 4,52</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-4,38; 8,17</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2,21; 13,74</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-5,91; 4,89</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-57,73; 73,57</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-37,45; 152,67</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>17,95; 866,25</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-71,03; 139,2</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-1.235349992531677</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>2.050580902632573</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>6.857476498959956</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-0.3851539024014257</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.1333100107752269</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.2401316784622587</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>2.255965378850571</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.06620038276985858</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>3,2</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-0,38</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,76</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,39</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>46,4%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-4,26%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-30,05%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>16,0%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-7.481521583735273</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-4.376889354440387</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>2.206676130007799</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-5.908627672044877</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.5772780713261721</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.3745140110690771</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>0.1795128954473952</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.71031375321687</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-4,07; 10,5</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-7,11; 6,95</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-6,99; 3,1</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-6,03; 8,71</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-43,36; 291,84</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-60,41; 128,95</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-80,39; 137,44</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-50,48; 169,0</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>4.524898091468194</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>8.166186945290137</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>13.74290761857437</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>4.893782012333871</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.7356913957268301</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1.526662515445368</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>8.662510572349985</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>1.392029234038713</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +817,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>8,92</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-3,82</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,84</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2,37</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>101,93%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-31,04%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>25,27%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>35,96%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>3.196698175415791</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.3769284742899726</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-1.755344004807896</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>1.389420523234292</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.4640041420195725</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.0426454674195238</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.3005065759358457</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.1599841193906203</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>0,65; 18,16</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-10,78; 3,42</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-3,92; 9,26</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-3,58; 9,93</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-1,24; 304,37</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-68,02; 43,69</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-44,48; 200,57</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-45,25; 276,33</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-4.071527633771772</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-7.108258633087476</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-6.986383765510264</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-6.029621079544908</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.4335891021539451</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.6041176355318424</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.803939613571233</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.5047754198207276</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>10.50274713302698</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>6.94749058421287</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>3.097993001367637</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>8.709899239100588</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>2.918436163764977</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>1.289516189408066</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>1.374397999109217</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>1.68998466625142</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>8.92097110294136</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-3.816366668992167</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>1.838766513164142</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>2.365700339542512</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>1.019302774029131</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.3103884353777545</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.252657059552966</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.3596180612338464</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.6495714472148707</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-10.77656309127124</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-3.919475397778205</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-3.583284908629248</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.01235254631843379</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.6802037235727869</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.4448032926861769</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.4525453817525187</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>18.16166311292239</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>3.422868633272173</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>9.258974825945689</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>9.930912084949647</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>3.043737655608048</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.4368820166190962</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>2.005698934844004</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>2.763269010482331</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>2,21</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,2</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2,49</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,89</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>22,06%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-2,0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>43,9%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>31,17%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-1,57; 5,99</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-3,53; 3,38</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-0,68; 5,7</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-1,33; 5,24</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-13,72; 74,04</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-31,73; 41,55</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-12,12; 130,64</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-19,25; 111,24</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>2.209443056719782</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.1977556594923366</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>2.492728158609042</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>1.887195992232203</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.2206185251206326</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.02002037255755853</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.4390193782586358</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.3117351041317086</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-1.570491495610452</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-3.526076092321337</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-0.6764356033568871</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-1.32959027572911</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.1372428689112504</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.3173231347679196</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.1211794955182598</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.1924690600990381</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>5.989583073221238</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>3.377810862091211</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>5.698356638025405</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>5.236165758937696</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.7404025857937637</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.415499378911945</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>1.306370642095557</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>1.112411933945461</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1115,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
